--- a/verification/cases/roundtrip/hyperlinks/init.xlsx
+++ b/verification/cases/roundtrip/hyperlinks/init.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48F20C9-E463-47E9-AE3A-2BE1EEC49331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22B7B7CA-A637-49CD-9BF5-FD343AB2C0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -357,33 +357,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.81640625" customWidth="1"/>
+    <col min="1" max="1" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
